--- a/data/Veridian_Master_Data_Pack_v1.xlsx
+++ b/data/Veridian_Master_Data_Pack_v1.xlsx
@@ -2,20 +2,21 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" r:id="Rd74ce162b0cc411a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Employees" sheetId="2" r:id="Rb7585cf4b11540ab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Departments" sheetId="3" r:id="Rff786705d84746db"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Teams" sheetId="4" r:id="Rd22eed2c3e294f97"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offices" sheetId="5" r:id="Rb2db81064b9f4c6b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Products" sheetId="6" r:id="R3980993c4ff84fa8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Systems" sheetId="7" r:id="R058ec89ed5984231"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Training Catalog" sheetId="8" r:id="R7cbb3f6e715c4ec4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Policies" sheetId="9" r:id="R7bfc9ba745ac4660"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Glossary" sheetId="10" r:id="R7b9f5f7cc98c40b8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FAQ" sheetId="11" r:id="R8f4c1992f7164634"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Career Levels" sheetId="12" r:id="R42ae7fb7cb3e492b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roles" sheetId="13" r:id="Rf3ce5db18e7d4106"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Headcount Summary" sheetId="14" r:id="Rcee32e1dfd9b4401"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" r:id="Rc67bc792c7e04238"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Employees" sheetId="2" r:id="R5d993d3cca514cee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Departments" sheetId="3" r:id="R17dc06e0639e4624"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Teams" sheetId="4" r:id="R6c50cc9326e64e53"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offices" sheetId="5" r:id="Rb7897a2478e040be"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Products" sheetId="6" r:id="R3e6fbc7aa23046b2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Systems" sheetId="7" r:id="Rb40a1751fe574152"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Training Catalog" sheetId="8" r:id="R849aa88d0e1f4c3a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Policies" sheetId="9" r:id="R9d0543c1e5a846b7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Glossary" sheetId="10" r:id="R5fc8f4b827d64ca6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FAQ" sheetId="11" r:id="Rb53b19a4c06049dd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Career Levels" sheetId="12" r:id="Rb764687ed9c64e82"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roles" sheetId="13" r:id="R6eb02419d3054818"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Headcount Summary" sheetId="14" r:id="Rb10222647d3d40bf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Role Catalog Additions" sheetId="15" r:id="Rcb265e4113a441db"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -43,7 +44,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="3">
+  <x:fills count="5">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -55,6 +56,16 @@
         <x:fgColor rgb="FF1F4E78"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEAF3F8"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="2">
     <x:border/>
@@ -63,7 +74,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="22">
+  <x:cellXfs count="28">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -117,6 +128,18 @@
     </x:xf>
     <x:xf numFmtId="202" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -604,7 +627,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R86d5e5786e49494a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2b004fc58e094d70"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -804,7 +827,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R77f3d6ddbf58433a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3e24c220a0bd48e3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1044,7 +1067,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ref95c202cc00491d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rab308b1c43e04d29"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1250,7 +1273,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rabee63f25a484447"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9149efe0bafb439f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2096,10 +2119,240 @@
         <x:v>See Training Catalog</x:v>
       </x:c>
     </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="27" t="str">
+        <x:v>ROLE-036</x:v>
+      </x:c>
+      <x:c r="B37" s="27" t="str">
+        <x:v>Engineering</x:v>
+      </x:c>
+      <x:c r="C37" s="27" t="str">
+        <x:v>Senior Integration Engineer</x:v>
+      </x:c>
+      <x:c r="D37" s="27" t="str">
+        <x:v>IC</x:v>
+      </x:c>
+      <x:c r="E37" s="27" t="str">
+        <x:v>IC4</x:v>
+      </x:c>
+      <x:c r="F37" s="27" t="str">
+        <x:v>Immediate team and manager</x:v>
+      </x:c>
+      <x:c r="G37" s="27" t="str">
+        <x:v>See Training Catalog</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="27" t="str">
+        <x:v>ROLE-037</x:v>
+      </x:c>
+      <x:c r="B38" s="27" t="str">
+        <x:v>Engineering</x:v>
+      </x:c>
+      <x:c r="C38" s="27" t="str">
+        <x:v>Integration Engineer</x:v>
+      </x:c>
+      <x:c r="D38" s="27" t="str">
+        <x:v>IC</x:v>
+      </x:c>
+      <x:c r="E38" s="27" t="str">
+        <x:v>IC3</x:v>
+      </x:c>
+      <x:c r="F38" s="27" t="str">
+        <x:v>Immediate team and manager</x:v>
+      </x:c>
+      <x:c r="G38" s="27" t="str">
+        <x:v>See Training Catalog</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="27" t="str">
+        <x:v>ROLE-038</x:v>
+      </x:c>
+      <x:c r="B39" s="27" t="str">
+        <x:v>Marketing</x:v>
+      </x:c>
+      <x:c r="C39" s="27" t="str">
+        <x:v>Marketing Manager</x:v>
+      </x:c>
+      <x:c r="D39" s="27" t="str">
+        <x:v>Manager</x:v>
+      </x:c>
+      <x:c r="E39" s="27" t="str">
+        <x:v>M2</x:v>
+      </x:c>
+      <x:c r="F39" s="27" t="str">
+        <x:v>Direct reports within assigned marketing sub-team, manager, immediate team</x:v>
+      </x:c>
+      <x:c r="G39" s="27" t="str">
+        <x:v>See Training Catalog</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" s="27" t="str">
+        <x:v>ROLE-039</x:v>
+      </x:c>
+      <x:c r="B40" s="27" t="str">
+        <x:v>Engineering</x:v>
+      </x:c>
+      <x:c r="C40" s="27" t="str">
+        <x:v>Full Stack Engineer</x:v>
+      </x:c>
+      <x:c r="D40" s="27" t="str">
+        <x:v>IC</x:v>
+      </x:c>
+      <x:c r="E40" s="27" t="str">
+        <x:v>IC3</x:v>
+      </x:c>
+      <x:c r="F40" s="27" t="str">
+        <x:v>Immediate team and manager</x:v>
+      </x:c>
+      <x:c r="G40" s="27" t="str">
+        <x:v>See Training Catalog</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" s="27" t="str">
+        <x:v>ROLE-040</x:v>
+      </x:c>
+      <x:c r="B41" s="27" t="str">
+        <x:v>Customer Success</x:v>
+      </x:c>
+      <x:c r="C41" s="27" t="str">
+        <x:v>Implementation Consultant</x:v>
+      </x:c>
+      <x:c r="D41" s="27" t="str">
+        <x:v>IC</x:v>
+      </x:c>
+      <x:c r="E41" s="27" t="str">
+        <x:v>IC3</x:v>
+      </x:c>
+      <x:c r="F41" s="27" t="str">
+        <x:v>Immediate team and manager</x:v>
+      </x:c>
+      <x:c r="G41" s="27" t="str">
+        <x:v>See Training Catalog</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" s="27" t="str">
+        <x:v>ROLE-041</x:v>
+      </x:c>
+      <x:c r="B42" s="27" t="str">
+        <x:v>Customer Success</x:v>
+      </x:c>
+      <x:c r="C42" s="27" t="str">
+        <x:v>Customer Support Specialist</x:v>
+      </x:c>
+      <x:c r="D42" s="27" t="str">
+        <x:v>IC</x:v>
+      </x:c>
+      <x:c r="E42" s="27" t="str">
+        <x:v>IC3</x:v>
+      </x:c>
+      <x:c r="F42" s="27" t="str">
+        <x:v>Immediate team and manager</x:v>
+      </x:c>
+      <x:c r="G42" s="27" t="str">
+        <x:v>See Training Catalog</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" s="27" t="str">
+        <x:v>ROLE-042</x:v>
+      </x:c>
+      <x:c r="B43" s="27" t="str">
+        <x:v>Marketing</x:v>
+      </x:c>
+      <x:c r="C43" s="27" t="str">
+        <x:v>Demand Generation Specialist</x:v>
+      </x:c>
+      <x:c r="D43" s="27" t="str">
+        <x:v>IC</x:v>
+      </x:c>
+      <x:c r="E43" s="27" t="str">
+        <x:v>IC3</x:v>
+      </x:c>
+      <x:c r="F43" s="27" t="str">
+        <x:v>Immediate team and manager</x:v>
+      </x:c>
+      <x:c r="G43" s="27" t="str">
+        <x:v>See Training Catalog</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" s="27" t="str">
+        <x:v>ROLE-043</x:v>
+      </x:c>
+      <x:c r="B44" s="27" t="str">
+        <x:v>Marketing</x:v>
+      </x:c>
+      <x:c r="C44" s="27" t="str">
+        <x:v>Marketing Analyst</x:v>
+      </x:c>
+      <x:c r="D44" s="27" t="str">
+        <x:v>IC</x:v>
+      </x:c>
+      <x:c r="E44" s="27" t="str">
+        <x:v>IC3</x:v>
+      </x:c>
+      <x:c r="F44" s="27" t="str">
+        <x:v>Immediate team and manager</x:v>
+      </x:c>
+      <x:c r="G44" s="27" t="str">
+        <x:v>See Training Catalog</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" s="27" t="str">
+        <x:v>ROLE-044</x:v>
+      </x:c>
+      <x:c r="B45" s="27" t="str">
+        <x:v>Engineering</x:v>
+      </x:c>
+      <x:c r="C45" s="27" t="str">
+        <x:v>Site Reliability Engineer</x:v>
+      </x:c>
+      <x:c r="D45" s="27" t="str">
+        <x:v>IC</x:v>
+      </x:c>
+      <x:c r="E45" s="27" t="str">
+        <x:v>IC3</x:v>
+      </x:c>
+      <x:c r="F45" s="27" t="str">
+        <x:v>Immediate team and manager</x:v>
+      </x:c>
+      <x:c r="G45" s="27" t="str">
+        <x:v>See Training Catalog</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" s="27" t="str">
+        <x:v>ROLE-045</x:v>
+      </x:c>
+      <x:c r="B46" s="27" t="str">
+        <x:v>Customer Success</x:v>
+      </x:c>
+      <x:c r="C46" s="27" t="str">
+        <x:v>Technical Support Engineer</x:v>
+      </x:c>
+      <x:c r="D46" s="27" t="str">
+        <x:v>IC</x:v>
+      </x:c>
+      <x:c r="E46" s="27" t="str">
+        <x:v>IC3</x:v>
+      </x:c>
+      <x:c r="F46" s="27" t="str">
+        <x:v>Immediate team and manager</x:v>
+      </x:c>
+      <x:c r="G46" s="27" t="str">
+        <x:v>See Training Catalog</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3c972439b8934648"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re7ba23cd011d419b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2259,8 +2512,683 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra0867ba1a0ab4522"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra42368a4a4ab4fa7"/>
   </x:tableParts>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="12" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="28" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="24" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="28" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="10" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="44" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="34" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="40" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="12" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="16" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="42" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="34" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="44" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="56" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="32" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="24" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="48" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="26" t="str">
+        <x:v>Role ID</x:v>
+      </x:c>
+      <x:c r="B1" s="26" t="str">
+        <x:v>Title</x:v>
+      </x:c>
+      <x:c r="C1" s="26" t="str">
+        <x:v>Department</x:v>
+      </x:c>
+      <x:c r="D1" s="26" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="E1" s="26" t="str">
+        <x:v>Team</x:v>
+      </x:c>
+      <x:c r="F1" s="26" t="str">
+        <x:v>Headcount</x:v>
+      </x:c>
+      <x:c r="G1" s="26" t="str">
+        <x:v>Employees / Examples</x:v>
+      </x:c>
+      <x:c r="H1" s="26" t="str">
+        <x:v>Manager(s)</x:v>
+      </x:c>
+      <x:c r="I1" s="26" t="str">
+        <x:v>Manager Email(s)</x:v>
+      </x:c>
+      <x:c r="J1" s="26" t="str">
+        <x:v>Track</x:v>
+      </x:c>
+      <x:c r="K1" s="26" t="str">
+        <x:v>Has Direct Reports</x:v>
+      </x:c>
+      <x:c r="L1" s="26" t="str">
+        <x:v>Direct Report Scope</x:v>
+      </x:c>
+      <x:c r="M1" s="26" t="str">
+        <x:v>Level / Seniority</x:v>
+      </x:c>
+      <x:c r="N1" s="26" t="str">
+        <x:v>Core Tools</x:v>
+      </x:c>
+      <x:c r="O1" s="26" t="str">
+        <x:v>Purpose</x:v>
+      </x:c>
+      <x:c r="P1" s="26" t="str">
+        <x:v>Responsibilities</x:v>
+      </x:c>
+      <x:c r="Q1" s="26" t="str">
+        <x:v>Interfaces / Collaboration</x:v>
+      </x:c>
+      <x:c r="R1" s="26" t="str">
+        <x:v>Mandatory Role Training</x:v>
+      </x:c>
+      <x:c r="S1" s="26" t="str">
+        <x:v>Data Boundary Notes</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="12" t="str">
+        <x:v>ROLE-036</x:v>
+      </x:c>
+      <x:c r="B2" s="12" t="str">
+        <x:v>Senior Integration Engineer</x:v>
+      </x:c>
+      <x:c r="C2" s="12" t="str">
+        <x:v>Engineering</x:v>
+      </x:c>
+      <x:c r="D2" s="12" t="str">
+        <x:v>Product Engineering</x:v>
+      </x:c>
+      <x:c r="E2" s="12" t="str">
+        <x:v>Connectors</x:v>
+      </x:c>
+      <x:c r="F2" s="12" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G2" s="12" t="str">
+        <x:v>Emily Morris; Gili Harari; Lior Peretz; Miguel Thomas; Roni Levin; Yoni Shor</x:v>
+      </x:c>
+      <x:c r="H2" s="12" t="str">
+        <x:v>Eitan Mor</x:v>
+      </x:c>
+      <x:c r="I2" s="12" t="str">
+        <x:v>eitan.mor@veridian.ai</x:v>
+      </x:c>
+      <x:c r="J2" s="12" t="str">
+        <x:v>IC</x:v>
+      </x:c>
+      <x:c r="K2" s="12" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="L2" s="12" t="str">
+        <x:v>No direct reports</x:v>
+      </x:c>
+      <x:c r="M2" s="12" t="str">
+        <x:v>IC4 / Senior</x:v>
+      </x:c>
+      <x:c r="N2" s="12" t="str">
+        <x:v>Jira; GitHub; Slack; Notion</x:v>
+      </x:c>
+      <x:c r="O2" s="12" t="str">
+        <x:v>Owns senior-level delivery of Veridian connector capabilities for Jira, GitHub, Slack and Notion.</x:v>
+      </x:c>
+      <x:c r="P2" s="12" t="str">
+        <x:v>Designs and develops connector features; improves reliability and maintainability of connector services; reviews integration-related pull requests; handles senior technical ownership within the Connectors team.</x:v>
+      </x:c>
+      <x:c r="Q2" s="12" t="str">
+        <x:v>Immediate team and manager</x:v>
+      </x:c>
+      <x:c r="R2" s="12" t="str">
+        <x:v>See Training Catalog</x:v>
+      </x:c>
+      <x:c r="S2" s="12" t="str">
+        <x:v>Org facts from provided role scope: Engineering / Connectors, manager Eitan Mor, IC with no direct reports.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="12" t="str">
+        <x:v>ROLE-037</x:v>
+      </x:c>
+      <x:c r="B3" s="12" t="str">
+        <x:v>Integration Engineer</x:v>
+      </x:c>
+      <x:c r="C3" s="12" t="str">
+        <x:v>Engineering</x:v>
+      </x:c>
+      <x:c r="D3" s="12" t="str">
+        <x:v>Product Engineering</x:v>
+      </x:c>
+      <x:c r="E3" s="12" t="str">
+        <x:v>Connectors</x:v>
+      </x:c>
+      <x:c r="F3" s="12" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G3" s="12" t="str">
+        <x:v>Eli Sasson; Elliot Carter; Rachel Clarke; Sofia White; Yair Shani</x:v>
+      </x:c>
+      <x:c r="H3" s="12" t="str">
+        <x:v>Eitan Mor</x:v>
+      </x:c>
+      <x:c r="I3" s="12" t="str">
+        <x:v>eitan.mor@veridian.ai</x:v>
+      </x:c>
+      <x:c r="J3" s="12" t="str">
+        <x:v>IC</x:v>
+      </x:c>
+      <x:c r="K3" s="12" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="L3" s="12" t="str">
+        <x:v>No direct reports</x:v>
+      </x:c>
+      <x:c r="M3" s="12" t="str">
+        <x:v>IC3 / Mid</x:v>
+      </x:c>
+      <x:c r="N3" s="12" t="str">
+        <x:v>Jira; GitHub; Slack; Notion</x:v>
+      </x:c>
+      <x:c r="O3" s="12" t="str">
+        <x:v>Builds and maintains connector capabilities used to connect Veridian with customer systems.</x:v>
+      </x:c>
+      <x:c r="P3" s="12" t="str">
+        <x:v>Implements connector functionality; fixes integration defects; contributes to code reviews and testing; supports delivery of Jira, GitHub, Slack and Notion connector work within the team.</x:v>
+      </x:c>
+      <x:c r="Q3" s="12" t="str">
+        <x:v>Immediate team and manager</x:v>
+      </x:c>
+      <x:c r="R3" s="12" t="str">
+        <x:v>See Training Catalog</x:v>
+      </x:c>
+      <x:c r="S3" s="12" t="str">
+        <x:v>Org facts from provided role scope: same team and manager as Senior Integration Engineer.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="12" t="str">
+        <x:v>ROLE-038</x:v>
+      </x:c>
+      <x:c r="B4" s="12" t="str">
+        <x:v>Marketing Manager</x:v>
+      </x:c>
+      <x:c r="C4" s="12" t="str">
+        <x:v>Marketing</x:v>
+      </x:c>
+      <x:c r="D4" s="12" t="str">
+        <x:v>Multiple marketing groups</x:v>
+      </x:c>
+      <x:c r="E4" s="12" t="str">
+        <x:v>Content &amp; Brand; Demand Generation; Marketing Operations; Product Marketing</x:v>
+      </x:c>
+      <x:c r="F4" s="12" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G4" s="12" t="str">
+        <x:v>Freya Walker; Avery Scott; Amitay Peleg; Roni Alon</x:v>
+      </x:c>
+      <x:c r="H4" s="12" t="str">
+        <x:v>Sophie Clarke (3 of 4); Adi Zohar (1 of 4)</x:v>
+      </x:c>
+      <x:c r="I4" s="12" t="str">
+        <x:v>sophie.clarke@veridian.ai; adi.zohar@veridian.ai</x:v>
+      </x:c>
+      <x:c r="J4" s="12" t="str">
+        <x:v>Manager</x:v>
+      </x:c>
+      <x:c r="K4" s="12" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="L4" s="12" t="str">
+        <x:v>Direct reports only within the same marketing sub-team; no cross-department reporting</x:v>
+      </x:c>
+      <x:c r="M4" s="12" t="str">
+        <x:v>M2 / Manager</x:v>
+      </x:c>
+      <x:c r="N4" s="12" t="str"/>
+      <x:c r="O4" s="12" t="str">
+        <x:v>Leads execution and people management within a defined marketing sub-team.</x:v>
+      </x:c>
+      <x:c r="P4" s="12" t="str">
+        <x:v>Translates marketing priorities into team-level plans; manages day-to-day execution; supports direct reports; coordinates work within the relevant marketing sub-team; escalates priorities and blockers to the relevant marketing leader.</x:v>
+      </x:c>
+      <x:c r="Q4" s="12" t="str">
+        <x:v>Manager, direct reports and immediate marketing sub-team</x:v>
+      </x:c>
+      <x:c r="R4" s="12" t="str">
+        <x:v>See Training Catalog</x:v>
+      </x:c>
+      <x:c r="S4" s="12" t="str">
+        <x:v>Managerial reporting facts from provided data: 3 report to Sophie Clarke and 1 reports to Adi Zohar; reporting does not cross departments.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="12" t="str">
+        <x:v>ROLE-039</x:v>
+      </x:c>
+      <x:c r="B5" s="12" t="str">
+        <x:v>Full Stack Engineer</x:v>
+      </x:c>
+      <x:c r="C5" s="12" t="str">
+        <x:v>Engineering</x:v>
+      </x:c>
+      <x:c r="D5" s="12" t="str">
+        <x:v>Product Engineering</x:v>
+      </x:c>
+      <x:c r="E5" s="12" t="str">
+        <x:v>Product Experience</x:v>
+      </x:c>
+      <x:c r="F5" s="12" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G5" s="12" t="str">
+        <x:v>Harper Rodriguez; Hila Shemesh; Lior Peleg</x:v>
+      </x:c>
+      <x:c r="H5" s="12" t="str">
+        <x:v>Dana Friedman</x:v>
+      </x:c>
+      <x:c r="I5" s="12" t="str">
+        <x:v>dana.friedman@veridian.ai</x:v>
+      </x:c>
+      <x:c r="J5" s="12" t="str">
+        <x:v>IC</x:v>
+      </x:c>
+      <x:c r="K5" s="12" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="L5" s="12" t="str">
+        <x:v>No direct reports</x:v>
+      </x:c>
+      <x:c r="M5" s="12" t="str">
+        <x:v>IC3 / Mid</x:v>
+      </x:c>
+      <x:c r="N5" s="12" t="str"/>
+      <x:c r="O5" s="12" t="str">
+        <x:v>Builds end-to-end product experience capabilities across frontend and backend surfaces.</x:v>
+      </x:c>
+      <x:c r="P5" s="12" t="str">
+        <x:v>Implements product-facing features; connects frontend behavior with backend services; participates in code reviews; supports quality and maintainability of Product Experience work.</x:v>
+      </x:c>
+      <x:c r="Q5" s="12" t="str">
+        <x:v>Immediate team and manager</x:v>
+      </x:c>
+      <x:c r="R5" s="12" t="str">
+        <x:v>See Training Catalog</x:v>
+      </x:c>
+      <x:c r="S5" s="12" t="str">
+        <x:v>Org facts from provided role scope: Engineering / Product Experience, manager Dana Friedman, IC with no direct reports. Tools were not specified in provided role data.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="12" t="str">
+        <x:v>ROLE-040</x:v>
+      </x:c>
+      <x:c r="B6" s="12" t="str">
+        <x:v>Implementation Consultant</x:v>
+      </x:c>
+      <x:c r="C6" s="12" t="str">
+        <x:v>Customer Success &amp; Support</x:v>
+      </x:c>
+      <x:c r="D6" s="12" t="str">
+        <x:v>Professional Services</x:v>
+      </x:c>
+      <x:c r="E6" s="12" t="str">
+        <x:v>Implementation</x:v>
+      </x:c>
+      <x:c r="F6" s="12" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G6" s="12" t="str">
+        <x:v>Caleb Howard; Emily Turner</x:v>
+      </x:c>
+      <x:c r="H6" s="12" t="str">
+        <x:v>Ido Regev</x:v>
+      </x:c>
+      <x:c r="I6" s="12" t="str">
+        <x:v>ido.regev2@veridian.ai</x:v>
+      </x:c>
+      <x:c r="J6" s="12" t="str">
+        <x:v>IC</x:v>
+      </x:c>
+      <x:c r="K6" s="12" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="L6" s="12" t="str">
+        <x:v>No direct reports</x:v>
+      </x:c>
+      <x:c r="M6" s="12" t="str">
+        <x:v>IC3 / Mid</x:v>
+      </x:c>
+      <x:c r="N6" s="12" t="str">
+        <x:v>Salesforce; Notion; Slack; Zendesk</x:v>
+      </x:c>
+      <x:c r="O6" s="12" t="str">
+        <x:v>Supports customer adoption during implementation and early rollout.</x:v>
+      </x:c>
+      <x:c r="P6" s="12" t="str">
+        <x:v>Guides customers through setup and implementation activities; documents adoption progress; answers implementation questions; coordinates customer-facing onboarding steps inside the Implementation team.</x:v>
+      </x:c>
+      <x:c r="Q6" s="12" t="str">
+        <x:v>Immediate team and manager</x:v>
+      </x:c>
+      <x:c r="R6" s="12" t="str">
+        <x:v>See Training Catalog</x:v>
+      </x:c>
+      <x:c r="S6" s="12" t="str">
+        <x:v>Manager is the Customer Success &amp; Support / Implementation Ido Regev record: ido.regev2@veridian.ai.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="12" t="str">
+        <x:v>ROLE-041</x:v>
+      </x:c>
+      <x:c r="B7" s="12" t="str">
+        <x:v>Customer Support Specialist</x:v>
+      </x:c>
+      <x:c r="C7" s="12" t="str">
+        <x:v>Customer Success &amp; Support</x:v>
+      </x:c>
+      <x:c r="D7" s="12" t="str">
+        <x:v>Support</x:v>
+      </x:c>
+      <x:c r="E7" s="12" t="str">
+        <x:v>Support</x:v>
+      </x:c>
+      <x:c r="F7" s="12" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G7" s="12" t="str">
+        <x:v>Itay Amar</x:v>
+      </x:c>
+      <x:c r="H7" s="12" t="str">
+        <x:v>Owen Rivera</x:v>
+      </x:c>
+      <x:c r="I7" s="12" t="str">
+        <x:v>owen.rivera@veridian.ai</x:v>
+      </x:c>
+      <x:c r="J7" s="12" t="str">
+        <x:v>IC</x:v>
+      </x:c>
+      <x:c r="K7" s="12" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="L7" s="12" t="str">
+        <x:v>No direct reports</x:v>
+      </x:c>
+      <x:c r="M7" s="12" t="str">
+        <x:v>IC3 / Mid</x:v>
+      </x:c>
+      <x:c r="N7" s="12" t="str">
+        <x:v>Salesforce; Notion; Slack; Zendesk</x:v>
+      </x:c>
+      <x:c r="O7" s="12" t="str">
+        <x:v>Handles customer support requests and contributes to customer adoption support.</x:v>
+      </x:c>
+      <x:c r="P7" s="12" t="str">
+        <x:v>Responds to customer support cases; documents resolutions; uses support systems to track issues; keeps customer-facing support information current for the Support team.</x:v>
+      </x:c>
+      <x:c r="Q7" s="12" t="str">
+        <x:v>Immediate team and manager</x:v>
+      </x:c>
+      <x:c r="R7" s="12" t="str">
+        <x:v>See Training Catalog</x:v>
+      </x:c>
+      <x:c r="S7" s="12" t="str">
+        <x:v>Org facts from provided role scope: Support team, manager Owen Rivera, peer of Technical Support Engineer.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="12" t="str">
+        <x:v>ROLE-042</x:v>
+      </x:c>
+      <x:c r="B8" s="12" t="str">
+        <x:v>Demand Generation Specialist</x:v>
+      </x:c>
+      <x:c r="C8" s="12" t="str">
+        <x:v>Marketing</x:v>
+      </x:c>
+      <x:c r="D8" s="12" t="str">
+        <x:v>Demand Generation</x:v>
+      </x:c>
+      <x:c r="E8" s="12" t="str">
+        <x:v>Demand Generation</x:v>
+      </x:c>
+      <x:c r="F8" s="12" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G8" s="12" t="str">
+        <x:v>Ava Scott</x:v>
+      </x:c>
+      <x:c r="H8" s="12" t="str">
+        <x:v>Avery Scott</x:v>
+      </x:c>
+      <x:c r="I8" s="12" t="str">
+        <x:v>avery.scott@veridian.ai</x:v>
+      </x:c>
+      <x:c r="J8" s="12" t="str">
+        <x:v>IC</x:v>
+      </x:c>
+      <x:c r="K8" s="12" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="L8" s="12" t="str">
+        <x:v>No direct reports</x:v>
+      </x:c>
+      <x:c r="M8" s="12" t="str">
+        <x:v>IC3 / Mid</x:v>
+      </x:c>
+      <x:c r="N8" s="12" t="str">
+        <x:v>HubSpot; Salesforce; Notion; Slack</x:v>
+      </x:c>
+      <x:c r="O8" s="12" t="str">
+        <x:v>Supports demand generation programs that create and nurture pipeline.</x:v>
+      </x:c>
+      <x:c r="P8" s="12" t="str">
+        <x:v>Executes campaign tasks; updates campaign assets and tracking; supports lead follow-up workflows; maintains campaign documentation and operational handoffs in the Demand Generation team.</x:v>
+      </x:c>
+      <x:c r="Q8" s="12" t="str">
+        <x:v>Immediate team and manager</x:v>
+      </x:c>
+      <x:c r="R8" s="12" t="str">
+        <x:v>See Training Catalog</x:v>
+      </x:c>
+      <x:c r="S8" s="12" t="str">
+        <x:v>Org facts from provided role scope: manager Avery Scott, tools HubSpot/Salesforce/Notion/Slack.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="12" t="str">
+        <x:v>ROLE-043</x:v>
+      </x:c>
+      <x:c r="B9" s="12" t="str">
+        <x:v>Marketing Analyst</x:v>
+      </x:c>
+      <x:c r="C9" s="12" t="str">
+        <x:v>Marketing</x:v>
+      </x:c>
+      <x:c r="D9" s="12" t="str">
+        <x:v>Marketing Operations</x:v>
+      </x:c>
+      <x:c r="E9" s="12" t="str">
+        <x:v>Marketing Operations</x:v>
+      </x:c>
+      <x:c r="F9" s="12" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G9" s="12" t="str">
+        <x:v>Moran Sela</x:v>
+      </x:c>
+      <x:c r="H9" s="12" t="str">
+        <x:v>Amitay Peleg</x:v>
+      </x:c>
+      <x:c r="I9" s="12" t="str">
+        <x:v>amitay.peleg@veridian.ai</x:v>
+      </x:c>
+      <x:c r="J9" s="12" t="str">
+        <x:v>IC</x:v>
+      </x:c>
+      <x:c r="K9" s="12" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="L9" s="12" t="str">
+        <x:v>No direct reports</x:v>
+      </x:c>
+      <x:c r="M9" s="12" t="str">
+        <x:v>IC3 / Mid</x:v>
+      </x:c>
+      <x:c r="N9" s="12" t="str">
+        <x:v>HubSpot; Salesforce; Notion; Slack</x:v>
+      </x:c>
+      <x:c r="O9" s="12" t="str">
+        <x:v>Supports marketing reporting and analysis for Marketing Operations.</x:v>
+      </x:c>
+      <x:c r="P9" s="12" t="str">
+        <x:v>Maintains marketing performance reporting; analyzes campaign and funnel data; prepares insights for marketing planning; supports operational data quality across marketing systems.</x:v>
+      </x:c>
+      <x:c r="Q9" s="12" t="str">
+        <x:v>Immediate team and manager</x:v>
+      </x:c>
+      <x:c r="R9" s="12" t="str">
+        <x:v>See Training Catalog</x:v>
+      </x:c>
+      <x:c r="S9" s="12" t="str">
+        <x:v>Org facts from provided role scope: manager Amitay Peleg, tools HubSpot/Salesforce/Notion/Slack.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="12" t="str">
+        <x:v>ROLE-044</x:v>
+      </x:c>
+      <x:c r="B10" s="12" t="str">
+        <x:v>Site Reliability Engineer</x:v>
+      </x:c>
+      <x:c r="C10" s="12" t="str">
+        <x:v>Engineering</x:v>
+      </x:c>
+      <x:c r="D10" s="12" t="str">
+        <x:v>Platform &amp; Security</x:v>
+      </x:c>
+      <x:c r="E10" s="12" t="str">
+        <x:v>Infrastructure &amp; DevOps</x:v>
+      </x:c>
+      <x:c r="F10" s="12" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G10" s="12" t="str">
+        <x:v>Dylan Brown</x:v>
+      </x:c>
+      <x:c r="H10" s="12" t="str">
+        <x:v>Nir Katz</x:v>
+      </x:c>
+      <x:c r="I10" s="12" t="str">
+        <x:v>nir.katz@veridian.ai</x:v>
+      </x:c>
+      <x:c r="J10" s="12" t="str">
+        <x:v>IC</x:v>
+      </x:c>
+      <x:c r="K10" s="12" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="L10" s="12" t="str">
+        <x:v>No direct reports</x:v>
+      </x:c>
+      <x:c r="M10" s="12" t="str">
+        <x:v>IC3 / Mid</x:v>
+      </x:c>
+      <x:c r="N10" s="12" t="str">
+        <x:v>Jira; GitHub; Slack; Notion</x:v>
+      </x:c>
+      <x:c r="O10" s="12" t="str">
+        <x:v>Supports reliability and operational stability for Veridian infrastructure.</x:v>
+      </x:c>
+      <x:c r="P10" s="12" t="str">
+        <x:v>Monitors service health; improves operational runbooks; contributes to incident response readiness; implements reliability improvements within Infrastructure &amp; DevOps.</x:v>
+      </x:c>
+      <x:c r="Q10" s="12" t="str">
+        <x:v>Immediate team and manager</x:v>
+      </x:c>
+      <x:c r="R10" s="12" t="str">
+        <x:v>See Training Catalog</x:v>
+      </x:c>
+      <x:c r="S10" s="12" t="str">
+        <x:v>Org facts from provided role scope: Engineering / Infrastructure &amp; DevOps, manager Nir Katz, IC with no direct reports.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="12" t="str">
+        <x:v>ROLE-045</x:v>
+      </x:c>
+      <x:c r="B11" s="12" t="str">
+        <x:v>Technical Support Engineer</x:v>
+      </x:c>
+      <x:c r="C11" s="12" t="str">
+        <x:v>Customer Success &amp; Support</x:v>
+      </x:c>
+      <x:c r="D11" s="12" t="str">
+        <x:v>Support</x:v>
+      </x:c>
+      <x:c r="E11" s="12" t="str">
+        <x:v>Support</x:v>
+      </x:c>
+      <x:c r="F11" s="12" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G11" s="12" t="str">
+        <x:v>Miguel Lewis</x:v>
+      </x:c>
+      <x:c r="H11" s="12" t="str">
+        <x:v>Owen Rivera</x:v>
+      </x:c>
+      <x:c r="I11" s="12" t="str">
+        <x:v>owen.rivera@veridian.ai</x:v>
+      </x:c>
+      <x:c r="J11" s="12" t="str">
+        <x:v>IC</x:v>
+      </x:c>
+      <x:c r="K11" s="12" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="L11" s="12" t="str">
+        <x:v>No direct reports</x:v>
+      </x:c>
+      <x:c r="M11" s="12" t="str">
+        <x:v>IC3 / Mid</x:v>
+      </x:c>
+      <x:c r="N11" s="12" t="str">
+        <x:v>Salesforce; Notion; Slack; Zendesk</x:v>
+      </x:c>
+      <x:c r="O11" s="12" t="str">
+        <x:v>Provides technical support for customer issues handled by the Support team.</x:v>
+      </x:c>
+      <x:c r="P11" s="12" t="str">
+        <x:v>Investigates technical support issues; documents findings and resolutions; uses support systems to manage cases; works as a peer to Customer Support Specialist under the same manager.</x:v>
+      </x:c>
+      <x:c r="Q11" s="12" t="str">
+        <x:v>Immediate team and manager</x:v>
+      </x:c>
+      <x:c r="R11" s="12" t="str">
+        <x:v>See Training Catalog</x:v>
+      </x:c>
+      <x:c r="S11" s="12" t="str">
+        <x:v>Org facts from provided role scope: same team and manager as Customer Support Specialist; peers, not a reporting chain.</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
 
@@ -19644,7 +20572,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7aaa116ab3244f55"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc7125837a9674a56"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -19864,7 +20792,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb02df2121e63481d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcb1c60c49a3d4589"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21072,7 +22000,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re5ae422d706a4ebd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rddadd86d360042cb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21198,7 +22126,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R34b362d1a89b4e3b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R17f2cb8d81fb4f44"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21318,7 +22246,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb16970ebaf7540ef"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcb2e687136a342cf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21558,7 +22486,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6966739c4b8e4dbe"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd73ccdb0de784fd7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21840,7 +22768,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb7ac010dd7c84393"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R546bf44b6fb7400d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -22000,7 +22928,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6278ef4054af4eb7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc28997542e50460c"/>
   </x:tableParts>
 </x:worksheet>
 </file>